--- a/htr-strucGenerale-CDA/ig/StructureDefinition-Prescription.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-Prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T10:35:11+00:00</t>
+    <t>2025-04-18T14:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-strucGenerale-CDA/ig/StructureDefinition-Prescription.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-Prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T14:53:38+00:00</t>
+    <t>2025-04-22T14:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -828,7 +828,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>78</v>
@@ -903,7 +903,7 @@
         <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>78</v>
